--- a/Side Bar Files/GWD Data/Gutter&Clamp.xlsx
+++ b/Side Bar Files/GWD Data/Gutter&Clamp.xlsx
@@ -370,23 +370,33 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -396,7 +406,9 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -844,7 +856,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6EB0DB1-B337-4491-81CA-5BE277E0B9A6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58FCB52E-CF50-4A9A-8C6A-2192203EB9A7}">
   <dimension ref="A1:F120"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>

--- a/Side Bar Files/GWD Data/Gutter&Clamp.xlsx
+++ b/Side Bar Files/GWD Data/Gutter&Clamp.xlsx
@@ -9,7 +9,13 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId3"/>
   </sheets>
-  <definedNames/>
+  <externalReferences>
+    <externalReference r:id="rId5"/>
+  </externalReferences>
+  <definedNames>
+    <definedName name="LMRRates">[1]LMR!$C:$C</definedName>
+    <definedName name="LMRCodes">[1]LMR!$A:$A</definedName>
+  </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -47,7 +53,7 @@
     <t>MATERIALS:</t>
   </si>
   <si>
-    <t>MR 10215</t>
+    <t>MR10215</t>
   </si>
   <si>
     <t>PVC Pipe, 6kg/cm2, 140mm Dia</t>
@@ -92,7 +98,7 @@
     <t>TOTAL  </t>
   </si>
   <si>
-    <t xml:space="preserve">Providing and fixing PVC gutter pipes includes laying jointing of pipes, complete as per direction of Engineer in Charge.for 160 mm dia 6 KGF/cm2 for 10m </t>
+    <t>Providing and fixing PVC gutter pipes includes laying jointing of pipes, complete as per direction of Engineer in Charge.for 160 mm dia 6 KGF/cm2</t>
   </si>
   <si>
     <t>MR10216</t>
@@ -101,13 +107,13 @@
     <t>PVC Pipe, 6kg/cm2, 160mm Dia</t>
   </si>
   <si>
-    <t xml:space="preserve">Providing and fixing 140mm square PVC  gutter pipes includes laying jointing of pipes   including clamp, complete as per direction of Engineer in Charge. for 10m </t>
+    <t>Providing and fixing 140mm square PVC gutter pipes includes laying jointing of pipes including clamp, complete as per direction of Engineer in Charge</t>
   </si>
   <si>
     <t xml:space="preserve">PVC pipe 140 mm square </t>
   </si>
   <si>
-    <t xml:space="preserve">Providing and fixing 160mm square PVC  gutter pipes includes laying jointing of pipes   including clamp, complete as per direction of Engineer in Charge. for 10m </t>
+    <t>Providing and fixing 160mm square PVC gutter pipes includes laying jointing of pipes including clamp, complete as per direction of Engineer in Charge</t>
   </si>
   <si>
     <t xml:space="preserve">PVC pipe 160 mm square </t>
@@ -116,7 +122,7 @@
     <t>Add 15% for fittings and wastage etc. on (A)</t>
   </si>
   <si>
-    <t xml:space="preserve">Providing and fixing MS Clamp for gutter pipe as per direction of Engineer in Charge. </t>
+    <t>Providing and fixing MS Clamp for gutter pipe as per direction of Engineer in Charge.</t>
   </si>
   <si>
     <t>Details of cost for 10 Nos</t>
@@ -340,25 +346,11 @@
       </bottom>
     </border>
   </borders>
-  <cellStyleXfs count="20">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment/>
       <protection/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -475,11 +467,11 @@
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="15" builtinId="5"/>
-    <cellStyle name="Currency" xfId="16" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="17" builtinId="7"/>
-    <cellStyle name="Comma" xfId="18" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="19" builtinId="6"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="3" builtinId="7"/>
+    <cellStyle name="Comma" xfId="4" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="5" builtinId="6"/>
   </cellStyles>
   <colors>
     <indexedColors>
@@ -558,6 +550,113 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="GWD DR Abstract"/>
+      <sheetName val="GWD MR Abstract"/>
+      <sheetName val="3 Core Cable PRICE"/>
+      <sheetName val="ARS Filter Media"/>
+      <sheetName val="BW Casing Pipes"/>
+      <sheetName val="Electrical Essentials"/>
+      <sheetName val="GI on Wall PRICE"/>
+      <sheetName val="GI wo Trench"/>
+      <sheetName val="GI With Trench PRICE"/>
+      <sheetName val="GI Works"/>
+      <sheetName val="Gravel for TWC"/>
+      <sheetName val="Gutter&amp;Clamp"/>
+      <sheetName val="HP Erection and Pullout"/>
+      <sheetName val="HP Repair Labour"/>
+      <sheetName val="HP Repair Spares"/>
+      <sheetName val="Hydrants"/>
+      <sheetName val="Iron Structure"/>
+      <sheetName val="Lock"/>
+      <sheetName val="Metallic PH"/>
+      <sheetName val="Motor Starter GWD"/>
+      <sheetName val="Motor Starter Monoblock"/>
+      <sheetName val="Motor Starter PRICE"/>
+      <sheetName val="Other Fittings PRICE"/>
+      <sheetName val="Panel Board"/>
+      <sheetName val="Pump Cover"/>
+      <sheetName val="Pump Erection "/>
+      <sheetName val="Pump Pullout"/>
+      <sheetName val="PVC Fittings"/>
+      <sheetName val="PVC Fittings PRICE"/>
+      <sheetName val="PVC on Wall (Concealed) PRICE"/>
+      <sheetName val="PVC on Wall PRICE"/>
+      <sheetName val="PVC on Wall"/>
+      <sheetName val="PVC wo Trench PRICE"/>
+      <sheetName val="PVC wo Trench"/>
+      <sheetName val="PVC With Trench PRICE"/>
+      <sheetName val="PVC With Trench"/>
+      <sheetName val="Scaffolding"/>
+      <sheetName val="Services"/>
+      <sheetName val="TW Casing Pipes"/>
+      <sheetName val="UG Cable PRICE"/>
+      <sheetName val="Water Meter"/>
+      <sheetName val="Water Tank"/>
+      <sheetName val="Well Protection"/>
+      <sheetName val="WTP"/>
+      <sheetName val="Derived"/>
+      <sheetName val="LMR"/>
+      <sheetName val="PAMR39"/>
+      <sheetName val="ZCost Index"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
+      <sheetData sheetId="17"/>
+      <sheetData sheetId="18"/>
+      <sheetData sheetId="19"/>
+      <sheetData sheetId="20"/>
+      <sheetData sheetId="21"/>
+      <sheetData sheetId="22"/>
+      <sheetData sheetId="23"/>
+      <sheetData sheetId="24"/>
+      <sheetData sheetId="25"/>
+      <sheetData sheetId="26"/>
+      <sheetData sheetId="27"/>
+      <sheetData sheetId="28"/>
+      <sheetData sheetId="29"/>
+      <sheetData sheetId="30"/>
+      <sheetData sheetId="31"/>
+      <sheetData sheetId="32"/>
+      <sheetData sheetId="33"/>
+      <sheetData sheetId="34"/>
+      <sheetData sheetId="35"/>
+      <sheetData sheetId="36"/>
+      <sheetData sheetId="37"/>
+      <sheetData sheetId="38"/>
+      <sheetData sheetId="39"/>
+      <sheetData sheetId="40"/>
+      <sheetData sheetId="41"/>
+      <sheetData sheetId="42"/>
+      <sheetData sheetId="43"/>
+      <sheetData sheetId="44"/>
+      <sheetData sheetId="45"/>
+      <sheetData sheetId="46"/>
+      <sheetData sheetId="47"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -856,7 +955,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58FCB52E-CF50-4A9A-8C6A-2192203EB9A7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD3D9E90-8A9F-40EE-B316-5048095CBAA6}">
   <dimension ref="A1:F120"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
@@ -936,11 +1035,12 @@
         <v>10.50</v>
       </c>
       <c r="E6" s="12">
-        <v>475</v>
+        <f t="array" ref="E6">IFERROR(INDEX(LMRRates,MATCH(A6,LMRCodes,0),),)</f>
+        <v>284</v>
       </c>
       <c r="F6" s="13">
         <f>D6*E6</f>
-        <v>4987.50</v>
+        <v>2982</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="12.75">
@@ -963,7 +1063,7 @@
       <c r="E8" s="7"/>
       <c r="F8" s="17">
         <f>SUM(F6:F7)</f>
-        <v>4987.50</v>
+        <v>2982</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="12.75">
@@ -976,7 +1076,7 @@
       <c r="E9" s="7"/>
       <c r="F9" s="17">
         <f>F8*0.01</f>
-        <v>49.875</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="12.75">
@@ -989,7 +1089,7 @@
       <c r="E10" s="7"/>
       <c r="F10" s="17">
         <f>F8+F9</f>
-        <v>5037.375</v>
+        <v>3011.82</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="12.75">
@@ -1002,7 +1102,7 @@
       <c r="E11" s="7"/>
       <c r="F11" s="17">
         <f>F10*0.15</f>
-        <v>755.60625000000005</v>
+        <v>451.77300000000002</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="12.75">
@@ -1015,7 +1115,7 @@
       <c r="E12" s="7"/>
       <c r="F12" s="17">
         <f>F10+F11</f>
-        <v>5792.9812499999998</v>
+        <v>3463.5929999999998</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="12.75">
@@ -1028,7 +1128,7 @@
       <c r="E13" s="7"/>
       <c r="F13" s="17">
         <f>F12</f>
-        <v>5792.9812499999998</v>
+        <v>3463.5929999999998</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="12.75">
@@ -1041,7 +1141,7 @@
       <c r="E14" s="7"/>
       <c r="F14" s="18">
         <f>ROUND((F13/10),2)</f>
-        <v>579.30</v>
+        <v>346.36</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="12.75">
@@ -1201,7 +1301,7 @@
     <row r="25" spans="1:6" ht="12.75">
       <c r="A25" s="21" t="str">
         <f>CONCATENATE("Say ₹ ",F14," + ",F24," x Cost Index")</f>
-        <v>Say ₹ 579.3 + 93.19 x Cost Index</v>
+        <v>Say ₹ 346.36 + 93.19 x Cost Index</v>
       </c>
       <c r="B25" s="6"/>
       <c r="C25" s="6"/>
@@ -1275,11 +1375,12 @@
         <v>10.50</v>
       </c>
       <c r="E30" s="27">
-        <v>613</v>
+        <f t="array" ref="E30">IFERROR(INDEX(LMRRates,MATCH(A30,LMRCodes,0),),)</f>
+        <v>372</v>
       </c>
       <c r="F30" s="28">
         <f>D30*E30</f>
-        <v>6436.50</v>
+        <v>3906</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="12.75">
@@ -1302,7 +1403,7 @@
       <c r="E32" s="7"/>
       <c r="F32" s="31">
         <f>SUM(F30:F31)</f>
-        <v>6436.50</v>
+        <v>3906</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="12.75">
@@ -1315,7 +1416,7 @@
       <c r="E33" s="7"/>
       <c r="F33" s="31">
         <f>F32*0.01</f>
-        <v>64.365</v>
+        <v>39.06</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="12.75">
@@ -1328,7 +1429,7 @@
       <c r="E34" s="7"/>
       <c r="F34" s="31">
         <f>F32+F33</f>
-        <v>6500.8649999999998</v>
+        <v>3945.06</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="12.75">
@@ -1341,7 +1442,7 @@
       <c r="E35" s="7"/>
       <c r="F35" s="31">
         <f>F34*0.15</f>
-        <v>975.12974999999994</v>
+        <v>591.75900000000001</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="12.75">
@@ -1354,7 +1455,7 @@
       <c r="E36" s="7"/>
       <c r="F36" s="31">
         <f>F34+F35</f>
-        <v>7475.9947499999998</v>
+        <v>4536.8190000000004</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="12.75">
@@ -1367,7 +1468,7 @@
       <c r="E37" s="7"/>
       <c r="F37" s="31">
         <f>F36</f>
-        <v>7475.9947499999998</v>
+        <v>4536.8190000000004</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="12.75">
@@ -1380,7 +1481,7 @@
       <c r="E38" s="7"/>
       <c r="F38" s="32">
         <f>ROUND((F37/10),2)</f>
-        <v>747.60</v>
+        <v>453.68</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="12.75">
@@ -1540,7 +1641,7 @@
     <row r="49" spans="1:6" ht="12.75">
       <c r="A49" s="35" t="str">
         <f>CONCATENATE("Say ₹ ",F38," + ",F48," x Cost Index")</f>
-        <v>Say ₹ 747.6 + 93.19 x Cost Index</v>
+        <v>Say ₹ 453.68 + 93.19 x Cost Index</v>
       </c>
       <c r="B49" s="6"/>
       <c r="C49" s="6"/>

--- a/Side Bar Files/GWD Data/Gutter&Clamp.xlsx
+++ b/Side Bar Files/GWD Data/Gutter&Clamp.xlsx
@@ -955,7 +955,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD3D9E90-8A9F-40EE-B316-5048095CBAA6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC48E14E-C111-462A-A4D0-993A5B7DBAA6}">
   <dimension ref="A1:F120"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>

--- a/Side Bar Files/GWD Data/Gutter&Clamp.xlsx
+++ b/Side Bar Files/GWD Data/Gutter&Clamp.xlsx
@@ -13,8 +13,8 @@
     <externalReference r:id="rId5"/>
   </externalReferences>
   <definedNames>
-    <definedName name="LMRRates">[1]LMR!$C:$C</definedName>
-    <definedName name="LMRCodes">[1]LMR!$A:$A</definedName>
+    <definedName name="LMRRates">[1]zLMR!$C:$C</definedName>
+    <definedName name="LMRCodes">[1]zLMR!$A:$A</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
@@ -600,10 +600,10 @@
       <sheetName val="Water Tank"/>
       <sheetName val="Well Protection"/>
       <sheetName val="WTP"/>
-      <sheetName val="Derived"/>
-      <sheetName val="LMR"/>
-      <sheetName val="PAMR39"/>
-      <sheetName val="ZCost Index"/>
+      <sheetName val="zCost Index"/>
+      <sheetName val="zDerived"/>
+      <sheetName val="zLMR"/>
+      <sheetName val="zPAMR39"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
@@ -955,7 +955,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC48E14E-C111-462A-A4D0-993A5B7DBAA6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{629F1768-06C9-41E0-B04C-6CD4F50BBAA6}">
   <dimension ref="A1:F120"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
